--- a/qtp_pyaez/data_input/crop_inputs/crop_specific_rule.xlsx
+++ b/qtp_pyaez/data_input/crop_inputs/crop_specific_rule.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ming-mayhu/Desktop/毕业论文/qtp-pyaez/qtp_pyaez/data_input/crop_inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1466178B-E6A5-5146-97F5-EC50B3D7EFBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7651928E-7093-2B47-A37A-FD6E4F7F8FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2780" yWindow="3780" windowWidth="25640" windowHeight="13980" xr2:uid="{FAED07CE-E758-F243-A6BC-F160777535F9}"/>
+    <workbookView xWindow="2780" yWindow="3040" windowWidth="25640" windowHeight="13980" xr2:uid="{FAED07CE-E758-F243-A6BC-F160777535F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="34">
   <si>
     <t>Crop</t>
   </si>
@@ -56,80 +56,95 @@
     <t>Not-Suitable</t>
   </si>
   <si>
-    <t>winter_wheat_59</t>
-  </si>
-  <si>
     <t>L6a</t>
   </si>
   <si>
     <t>≤</t>
   </si>
   <si>
-    <t>0.5×CYb</t>
-  </si>
-  <si>
-    <t>0.667×CYb</t>
-  </si>
-  <si>
-    <t>winter_wheat_60</t>
-  </si>
-  <si>
     <t>L6b</t>
   </si>
   <si>
-    <t>winter_wheat_61</t>
-  </si>
-  <si>
     <t>L2a+L2b</t>
   </si>
   <si>
-    <t>0.333×CYb</t>
-  </si>
-  <si>
-    <t>0.4×CYb</t>
-  </si>
-  <si>
-    <t>winter_wheat_62</t>
-  </si>
-  <si>
     <t>L1a+L1b</t>
   </si>
   <si>
-    <t>winter_wheat_63</t>
-  </si>
-  <si>
     <t>L2b+L3b+L4b+L5b</t>
   </si>
   <si>
-    <t>winter_wheat_64</t>
-  </si>
-  <si>
-    <t>N3b+N4b+N5b+N6b-(L3b+L4b+L5b)</t>
-  </si>
-  <si>
     <t>≥</t>
   </si>
   <si>
-    <t>CYa</t>
-  </si>
-  <si>
-    <t>winter_wheat_65</t>
-  </si>
-  <si>
-    <t>Dormancy*</t>
-  </si>
-  <si>
-    <t>winter_wheat_66</t>
-  </si>
-  <si>
-    <t>Vernalization**</t>
+    <t>winter_barley_59</t>
+  </si>
+  <si>
+    <t>winter_barley_60</t>
+  </si>
+  <si>
+    <t>winter_barley_61</t>
+  </si>
+  <si>
+    <t>winter_barley_62</t>
+  </si>
+  <si>
+    <t>0.5*CYb</t>
+  </si>
+  <si>
+    <t>0.667*CYb</t>
+  </si>
+  <si>
+    <t>0.333*CYb</t>
+  </si>
+  <si>
+    <t>0.4*CYb</t>
+  </si>
+  <si>
+    <t>L6a+L5a</t>
+  </si>
+  <si>
+    <t>L4a+L3a+L2a+L2b+L3b+L4b</t>
+  </si>
+  <si>
+    <t>L2b+L3b+L4b+L5b+L6b</t>
+  </si>
+  <si>
+    <t>spring_barley_63</t>
+  </si>
+  <si>
+    <t>spring_barley_64</t>
+  </si>
+  <si>
+    <t>spring_barley_65</t>
+  </si>
+  <si>
+    <t>spring_barley_66</t>
+  </si>
+  <si>
+    <t>0.375*CY</t>
+  </si>
+  <si>
+    <t>0.500*CY</t>
+  </si>
+  <si>
+    <t>0.167*CY</t>
+  </si>
+  <si>
+    <t>0.0835*CY</t>
+  </si>
+  <si>
+    <t>0.333*CY</t>
+  </si>
+  <si>
+    <t>0.667*CY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -147,6 +162,31 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -170,10 +210,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -508,8 +557,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0741791B-D8B1-7142-B84F-2E444F66886B}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="28.33203125" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -533,33 +586,33 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
@@ -576,30 +629,30 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
@@ -613,69 +666,1115 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" t="s">
+        <v>29</v>
+      </c>
+      <c r="F29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" t="s">
+        <v>31</v>
+      </c>
+      <c r="F31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" t="s">
+        <v>32</v>
+      </c>
+      <c r="F32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" t="s">
+        <v>29</v>
+      </c>
+      <c r="F33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" t="s">
+        <v>29</v>
+      </c>
+      <c r="F35" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B36" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" t="s">
+        <v>28</v>
+      </c>
+      <c r="E36" t="s">
+        <v>29</v>
+      </c>
+      <c r="F36" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" t="s">
+        <v>30</v>
+      </c>
+      <c r="E38" t="s">
+        <v>31</v>
+      </c>
+      <c r="F38" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" t="s">
+        <v>32</v>
+      </c>
+      <c r="F39" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B40" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" t="s">
+        <v>33</v>
+      </c>
+      <c r="E40" t="s">
+        <v>29</v>
+      </c>
+      <c r="F40" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B41" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" t="s">
+        <v>29</v>
+      </c>
+      <c r="E42" t="s">
+        <v>29</v>
+      </c>
+      <c r="F42" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B43" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="E43" t="s">
+        <v>29</v>
+      </c>
+      <c r="F43" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B44" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B45" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" t="s">
+        <v>30</v>
+      </c>
+      <c r="E45" t="s">
+        <v>31</v>
+      </c>
+      <c r="F45" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B46" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" t="s">
+        <v>32</v>
+      </c>
+      <c r="E46" t="s">
+        <v>32</v>
+      </c>
+      <c r="F46" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B47" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" t="s">
+        <v>33</v>
+      </c>
+      <c r="E47" t="s">
+        <v>29</v>
+      </c>
+      <c r="F47" t="s">
+        <v>32</v>
+      </c>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="5"/>
+      <c r="M47" s="5"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
+      <c r="M48" s="5"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B49" t="s">
+        <v>23</v>
+      </c>
+      <c r="C49" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" t="s">
+        <v>29</v>
+      </c>
+      <c r="E49" t="s">
+        <v>29</v>
+      </c>
+      <c r="F49" t="s">
+        <v>29</v>
+      </c>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5"/>
+      <c r="K49" s="5"/>
+      <c r="L49" s="5"/>
+      <c r="M49" s="5"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A50" s="1"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="6"/>
+      <c r="L50" s="6"/>
+      <c r="M50" s="6"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A51" s="1"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6"/>
+      <c r="L51" s="6"/>
+      <c r="M51" s="6"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A52" s="1"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="7"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="6"/>
+      <c r="M52" s="6"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A53" s="1"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="7"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
+      <c r="K53" s="6"/>
+      <c r="L53" s="6"/>
+      <c r="M53" s="6"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A54" s="1"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="6"/>
+      <c r="M54" s="6"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A55" s="1"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
+      <c r="K55" s="6"/>
+      <c r="L55" s="6"/>
+      <c r="M55" s="6"/>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A56" s="1"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
+      <c r="K56" s="6"/>
+      <c r="L56" s="6"/>
+      <c r="M56" s="6"/>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A57" s="1"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="6"/>
+      <c r="K57" s="6"/>
+      <c r="L57" s="6"/>
+      <c r="M57" s="6"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A58" s="1"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="6"/>
+      <c r="L58" s="6"/>
+      <c r="M58" s="6"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A59" s="1"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="7"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="6"/>
+      <c r="M59" s="6"/>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A60" s="3"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="6"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A61" s="3"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="7"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="6"/>
+      <c r="K61" s="6"/>
+      <c r="L61" s="6"/>
+      <c r="M61" s="6"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A62" s="3"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="5"/>
+      <c r="J62" s="5"/>
+      <c r="K62" s="5"/>
+      <c r="L62" s="5"/>
+      <c r="M62" s="5"/>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A63" s="3"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5"/>
+      <c r="J63" s="5"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="5"/>
+      <c r="M63" s="5"/>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A64" s="3"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A65" s="3"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A66" s="3"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A67" s="3"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A68" s="3"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A69" s="3"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/qtp_pyaez/data_input/crop_inputs/crop_specific_rule.xlsx
+++ b/qtp_pyaez/data_input/crop_inputs/crop_specific_rule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ming-mayhu/Desktop/毕业论文/qtp-pyaez/qtp_pyaez/data_input/crop_inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7651928E-7093-2B47-A37A-FD6E4F7F8FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A95AFA0-1B18-0B49-87A3-63540D1E6164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2780" yWindow="3040" windowWidth="25640" windowHeight="13980" xr2:uid="{FAED07CE-E758-F243-A6BC-F160777535F9}"/>
+    <workbookView xWindow="1460" yWindow="680" windowWidth="25640" windowHeight="13980" xr2:uid="{FAED07CE-E758-F243-A6BC-F160777535F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="43">
   <si>
     <t>Crop</t>
   </si>
@@ -138,13 +138,40 @@
   </si>
   <si>
     <t>0.667*CY</t>
+  </si>
+  <si>
+    <t>winter_wheat_1</t>
+  </si>
+  <si>
+    <t>winter_wheat_2</t>
+  </si>
+  <si>
+    <t>winter_wheat_3</t>
+  </si>
+  <si>
+    <t>winter_wheat_4</t>
+  </si>
+  <si>
+    <t>spring_wheat_5</t>
+  </si>
+  <si>
+    <t>spring_wheat_6</t>
+  </si>
+  <si>
+    <t>spring_wheat_7</t>
+  </si>
+  <si>
+    <t>spring_wheat_8</t>
+  </si>
+  <si>
+    <t>spring_wheat_9</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -176,19 +203,6 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -210,17 +224,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -557,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0741791B-D8B1-7142-B84F-2E444F66886B}">
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M104"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.33203125" customWidth="1"/>
@@ -1204,7 +1215,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>25</v>
       </c>
@@ -1224,7 +1235,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>25</v>
       </c>
@@ -1244,7 +1255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>25</v>
       </c>
@@ -1264,7 +1275,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>26</v>
       </c>
@@ -1284,7 +1295,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>26</v>
       </c>
@@ -1304,7 +1315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>26</v>
       </c>
@@ -1324,7 +1335,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>26</v>
       </c>
@@ -1344,7 +1355,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>26</v>
       </c>
@@ -1364,7 +1375,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>26</v>
       </c>
@@ -1384,7 +1395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>26</v>
       </c>
@@ -1404,7 +1415,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>27</v>
       </c>
@@ -1424,7 +1435,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>27</v>
       </c>
@@ -1444,7 +1455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>27</v>
       </c>
@@ -1464,7 +1475,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>27</v>
       </c>
@@ -1484,7 +1495,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>27</v>
       </c>
@@ -1503,15 +1514,8 @@
       <c r="F47" t="s">
         <v>32</v>
       </c>
-      <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
-      <c r="I47" s="5"/>
-      <c r="J47" s="5"/>
-      <c r="K47" s="5"/>
-      <c r="L47" s="5"/>
-      <c r="M47" s="5"/>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>27</v>
       </c>
@@ -1530,13 +1534,6 @@
       <c r="F48">
         <v>0</v>
       </c>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
-      <c r="I48" s="5"/>
-      <c r="J48" s="5"/>
-      <c r="K48" s="5"/>
-      <c r="L48" s="5"/>
-      <c r="M48" s="5"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
@@ -1557,221 +1554,1146 @@
       <c r="F49" t="s">
         <v>29</v>
       </c>
-      <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
-      <c r="I49" s="5"/>
-      <c r="J49" s="5"/>
-      <c r="K49" s="5"/>
-      <c r="L49" s="5"/>
-      <c r="M49" s="5"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" s="1"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="6"/>
-      <c r="L50" s="6"/>
-      <c r="M50" s="6"/>
+      <c r="A50" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" s="1"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="3"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A51" s="1"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="6"/>
-      <c r="L51" s="6"/>
-      <c r="M51" s="6"/>
+      <c r="A51" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" s="3">
+        <v>0</v>
+      </c>
+      <c r="E51" s="3">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="3"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" s="1"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="7"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6"/>
-      <c r="L52" s="6"/>
-      <c r="M52" s="6"/>
+      <c r="A52" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F52" t="s">
+        <v>19</v>
+      </c>
+      <c r="G52" s="1"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="3"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A53" s="1"/>
-      <c r="G53" s="5"/>
-      <c r="H53" s="7"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
-      <c r="K53" s="6"/>
-      <c r="L53" s="6"/>
-      <c r="M53" s="6"/>
+      <c r="A53" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" s="3">
+        <v>0</v>
+      </c>
+      <c r="E53" s="3">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="3"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A54" s="1"/>
-      <c r="G54" s="5"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6"/>
-      <c r="L54" s="6"/>
-      <c r="M54" s="6"/>
+      <c r="A54" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F54" t="s">
+        <v>17</v>
+      </c>
+      <c r="G54" s="1"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="3"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A55" s="1"/>
-      <c r="G55" s="5"/>
-      <c r="H55" s="7"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="6"/>
-      <c r="K55" s="6"/>
-      <c r="L55" s="6"/>
-      <c r="M55" s="6"/>
+      <c r="A55" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F55" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" s="1"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="3"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A56" s="1"/>
-      <c r="G56" s="5"/>
-      <c r="H56" s="7"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
-      <c r="K56" s="6"/>
-      <c r="L56" s="6"/>
-      <c r="M56" s="6"/>
+      <c r="A56" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" s="3">
+        <v>0</v>
+      </c>
+      <c r="E56" s="3">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3"/>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A57" s="1"/>
-      <c r="G57" s="5"/>
-      <c r="H57" s="7"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="6"/>
-      <c r="K57" s="6"/>
-      <c r="L57" s="6"/>
-      <c r="M57" s="6"/>
+      <c r="A57" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F57" t="s">
+        <v>19</v>
+      </c>
+      <c r="G57" s="1"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3"/>
+      <c r="K57" s="3"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A58" s="1"/>
-      <c r="G58" s="5"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="6"/>
-      <c r="K58" s="6"/>
-      <c r="L58" s="6"/>
-      <c r="M58" s="6"/>
+      <c r="A58" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="H58" s="4"/>
+      <c r="I58" s="3"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A59" s="1"/>
-      <c r="G59" s="5"/>
-      <c r="H59" s="7"/>
-      <c r="I59" s="6"/>
-      <c r="J59" s="6"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="6"/>
-      <c r="M59" s="6"/>
+      <c r="A59" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F59" t="s">
+        <v>17</v>
+      </c>
+      <c r="H59" s="4"/>
+      <c r="I59" s="3"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A60" s="3"/>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="5"/>
-      <c r="H60" s="7"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
-      <c r="K60" s="6"/>
-      <c r="L60" s="6"/>
-      <c r="M60" s="6"/>
+      <c r="A60" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+      <c r="H60" s="4"/>
+      <c r="I60" s="3"/>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A61" s="3"/>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
-      <c r="G61" s="5"/>
-      <c r="H61" s="7"/>
-      <c r="I61" s="6"/>
-      <c r="J61" s="6"/>
-      <c r="K61" s="6"/>
-      <c r="L61" s="6"/>
-      <c r="M61" s="6"/>
+      <c r="A61" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="H61" s="4"/>
+      <c r="I61" s="3"/>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A62" s="3"/>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="5"/>
-      <c r="H62" s="5"/>
-      <c r="I62" s="5"/>
-      <c r="J62" s="5"/>
-      <c r="K62" s="5"/>
-      <c r="L62" s="5"/>
-      <c r="M62" s="5"/>
+      <c r="A62" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F62" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A63" s="3"/>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
-      <c r="I63" s="5"/>
-      <c r="J63" s="5"/>
-      <c r="K63" s="5"/>
-      <c r="L63" s="5"/>
-      <c r="M63" s="5"/>
+      <c r="A63" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" s="3">
+        <v>0</v>
+      </c>
+      <c r="E63" s="3">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A64" s="3"/>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
+      <c r="A64" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F64" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A65" s="3"/>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4"/>
+      <c r="A65" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F65" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A66" s="3"/>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="4"/>
+      <c r="A66" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66" s="3">
+        <v>0</v>
+      </c>
+      <c r="E66" s="3">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A67" s="3"/>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
+      <c r="A67" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F67" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A68" s="3"/>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
+      <c r="A68" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" s="3">
+        <v>0</v>
+      </c>
+      <c r="E68" s="3">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A69" s="3"/>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
+      <c r="A69" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F69" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F70" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D71" s="3">
+        <v>0</v>
+      </c>
+      <c r="E71" s="3">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F72" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A73" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F73" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B74" t="s">
+        <v>22</v>
+      </c>
+      <c r="C74" t="s">
+        <v>12</v>
+      </c>
+      <c r="D74" t="s">
+        <v>33</v>
+      </c>
+      <c r="E74" t="s">
+        <v>29</v>
+      </c>
+      <c r="F74" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B75" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" t="s">
+        <v>7</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B76" t="s">
+        <v>23</v>
+      </c>
+      <c r="C76" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76" t="s">
+        <v>29</v>
+      </c>
+      <c r="E76" t="s">
+        <v>29</v>
+      </c>
+      <c r="F76" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A77" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F77" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A78" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D78" s="3">
+        <v>0</v>
+      </c>
+      <c r="E78" s="3">
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A79" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F79" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A80" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F80" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A81" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B81" t="s">
+        <v>22</v>
+      </c>
+      <c r="C81" t="s">
+        <v>12</v>
+      </c>
+      <c r="D81" t="s">
+        <v>33</v>
+      </c>
+      <c r="E81" t="s">
+        <v>29</v>
+      </c>
+      <c r="F81" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A82" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B82" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82" t="s">
+        <v>7</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A83" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B83" t="s">
+        <v>23</v>
+      </c>
+      <c r="C83" t="s">
+        <v>7</v>
+      </c>
+      <c r="D83" t="s">
+        <v>29</v>
+      </c>
+      <c r="E83" t="s">
+        <v>29</v>
+      </c>
+      <c r="F83" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A84" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F84" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A85" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D85" s="3">
+        <v>0</v>
+      </c>
+      <c r="E85" s="3">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A86" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F86" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A87" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F87" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A88" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B88" t="s">
+        <v>22</v>
+      </c>
+      <c r="C88" t="s">
+        <v>12</v>
+      </c>
+      <c r="D88" t="s">
+        <v>33</v>
+      </c>
+      <c r="E88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F88" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A89" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B89" t="s">
+        <v>10</v>
+      </c>
+      <c r="C89" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A90" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B90" t="s">
+        <v>23</v>
+      </c>
+      <c r="C90" t="s">
+        <v>7</v>
+      </c>
+      <c r="D90" t="s">
+        <v>29</v>
+      </c>
+      <c r="E90" t="s">
+        <v>29</v>
+      </c>
+      <c r="F90" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A91" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F91" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A92" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D92" s="3">
+        <v>0</v>
+      </c>
+      <c r="E92" s="3">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A93" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F93" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A94" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F94" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A95" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B95" t="s">
+        <v>22</v>
+      </c>
+      <c r="C95" t="s">
+        <v>12</v>
+      </c>
+      <c r="D95" t="s">
+        <v>33</v>
+      </c>
+      <c r="E95" t="s">
+        <v>29</v>
+      </c>
+      <c r="F95" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A96" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B96" t="s">
+        <v>10</v>
+      </c>
+      <c r="C96" t="s">
+        <v>7</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A97" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B97" t="s">
+        <v>23</v>
+      </c>
+      <c r="C97" t="s">
+        <v>7</v>
+      </c>
+      <c r="D97" t="s">
+        <v>29</v>
+      </c>
+      <c r="E97" t="s">
+        <v>29</v>
+      </c>
+      <c r="F97" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A98" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F98" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A99" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D99" s="3">
+        <v>0</v>
+      </c>
+      <c r="E99" s="3">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A100" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F100" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A101" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F101" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A102" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B102" t="s">
+        <v>22</v>
+      </c>
+      <c r="C102" t="s">
+        <v>12</v>
+      </c>
+      <c r="D102" t="s">
+        <v>33</v>
+      </c>
+      <c r="E102" t="s">
+        <v>29</v>
+      </c>
+      <c r="F102" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A103" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B103" t="s">
+        <v>10</v>
+      </c>
+      <c r="C103" t="s">
+        <v>7</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A104" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B104" t="s">
+        <v>23</v>
+      </c>
+      <c r="C104" t="s">
+        <v>7</v>
+      </c>
+      <c r="D104" t="s">
+        <v>29</v>
+      </c>
+      <c r="E104" t="s">
+        <v>29</v>
+      </c>
+      <c r="F104" t="s">
+        <v>29</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/qtp_pyaez/data_input/crop_inputs/crop_specific_rule.xlsx
+++ b/qtp_pyaez/data_input/crop_inputs/crop_specific_rule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ming-mayhu/Desktop/毕业论文/qtp-pyaez/qtp_pyaez/data_input/crop_inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A95AFA0-1B18-0B49-87A3-63540D1E6164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9323D3A7-2CDA-8D4A-9C29-6D1D3F02CAC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="680" windowWidth="25640" windowHeight="13980" xr2:uid="{FAED07CE-E758-F243-A6BC-F160777535F9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="61">
   <si>
     <t>Crop</t>
   </si>
@@ -165,13 +165,67 @@
   </si>
   <si>
     <t>spring_wheat_9</t>
+  </si>
+  <si>
+    <t>L6a+L6b</t>
+  </si>
+  <si>
+    <t>L5a+L5b</t>
+  </si>
+  <si>
+    <t>silage_maize_53</t>
+  </si>
+  <si>
+    <t>silage_maize_54</t>
+  </si>
+  <si>
+    <t>silage_maize_55</t>
+  </si>
+  <si>
+    <t>silage_maize_56</t>
+  </si>
+  <si>
+    <t>silage_maize_57</t>
+  </si>
+  <si>
+    <t>silage_maize_58</t>
+  </si>
+  <si>
+    <t>white_potato_135</t>
+  </si>
+  <si>
+    <t>white_potato_136</t>
+  </si>
+  <si>
+    <t>white_potato_137</t>
+  </si>
+  <si>
+    <t>white_potato_138</t>
+  </si>
+  <si>
+    <t>white_potato_139</t>
+  </si>
+  <si>
+    <t>white_potato_140</t>
+  </si>
+  <si>
+    <t>white_potato_141</t>
+  </si>
+  <si>
+    <t>L6a+L5a+L4a+L4b+L5b+L6b</t>
+  </si>
+  <si>
+    <t>0.000*CY</t>
+  </si>
+  <si>
+    <t>0.083*CY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -203,6 +257,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -224,7 +285,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -232,6 +293,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -568,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0741791B-D8B1-7142-B84F-2E444F66886B}">
-  <dimension ref="A1:M104"/>
+  <dimension ref="A1:M163"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.33203125" customWidth="1"/>
@@ -2535,7 +2603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>41</v>
       </c>
@@ -2555,7 +2623,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>42</v>
       </c>
@@ -2575,7 +2643,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
         <v>42</v>
       </c>
@@ -2595,7 +2663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
         <v>42</v>
       </c>
@@ -2615,7 +2683,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>42</v>
       </c>
@@ -2635,7 +2703,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
         <v>42</v>
       </c>
@@ -2655,7 +2723,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>42</v>
       </c>
@@ -2675,7 +2743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>42</v>
       </c>
@@ -2693,6 +2761,1246 @@
       </c>
       <c r="F104" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>45</v>
+      </c>
+      <c r="B105" t="s">
+        <v>43</v>
+      </c>
+      <c r="C105" t="s">
+        <v>7</v>
+      </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>45</v>
+      </c>
+      <c r="B106" t="s">
+        <v>44</v>
+      </c>
+      <c r="C106" t="s">
+        <v>7</v>
+      </c>
+      <c r="D106" t="s">
+        <v>29</v>
+      </c>
+      <c r="E106" t="s">
+        <v>33</v>
+      </c>
+      <c r="F106" t="s">
+        <v>33</v>
+      </c>
+      <c r="H106" s="5"/>
+      <c r="I106" s="5"/>
+      <c r="J106" s="5"/>
+      <c r="K106" s="5"/>
+      <c r="L106" s="5"/>
+      <c r="M106" s="5"/>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>45</v>
+      </c>
+      <c r="B107" t="s">
+        <v>9</v>
+      </c>
+      <c r="C107" t="s">
+        <v>7</v>
+      </c>
+      <c r="D107" t="s">
+        <v>32</v>
+      </c>
+      <c r="E107" t="s">
+        <v>29</v>
+      </c>
+      <c r="F107" t="s">
+        <v>29</v>
+      </c>
+      <c r="H107" s="7"/>
+      <c r="I107" s="6"/>
+      <c r="J107" s="6"/>
+      <c r="K107" s="6"/>
+      <c r="L107" s="6"/>
+      <c r="M107" s="6"/>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>45</v>
+      </c>
+      <c r="B108" t="s">
+        <v>10</v>
+      </c>
+      <c r="C108" t="s">
+        <v>7</v>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+      <c r="F108">
+        <v>0</v>
+      </c>
+      <c r="H108" s="7"/>
+      <c r="I108" s="6"/>
+      <c r="J108" s="6"/>
+      <c r="K108" s="6"/>
+      <c r="L108" s="6"/>
+      <c r="M108" s="6"/>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>46</v>
+      </c>
+      <c r="B109" t="s">
+        <v>43</v>
+      </c>
+      <c r="C109" t="s">
+        <v>7</v>
+      </c>
+      <c r="D109">
+        <v>0</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109">
+        <v>0</v>
+      </c>
+      <c r="H109" s="7"/>
+      <c r="I109" s="6"/>
+      <c r="J109" s="6"/>
+      <c r="K109" s="6"/>
+      <c r="L109" s="6"/>
+      <c r="M109" s="6"/>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>46</v>
+      </c>
+      <c r="B110" t="s">
+        <v>44</v>
+      </c>
+      <c r="C110" t="s">
+        <v>7</v>
+      </c>
+      <c r="D110" t="s">
+        <v>29</v>
+      </c>
+      <c r="E110" t="s">
+        <v>33</v>
+      </c>
+      <c r="F110" t="s">
+        <v>33</v>
+      </c>
+      <c r="H110" s="7"/>
+      <c r="I110" s="6"/>
+      <c r="J110" s="6"/>
+      <c r="K110" s="6"/>
+      <c r="L110" s="6"/>
+      <c r="M110" s="6"/>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>46</v>
+      </c>
+      <c r="B111" t="s">
+        <v>9</v>
+      </c>
+      <c r="C111" t="s">
+        <v>7</v>
+      </c>
+      <c r="D111" t="s">
+        <v>32</v>
+      </c>
+      <c r="E111" t="s">
+        <v>29</v>
+      </c>
+      <c r="F111" t="s">
+        <v>29</v>
+      </c>
+      <c r="H111" s="5"/>
+      <c r="I111" s="5"/>
+      <c r="J111" s="5"/>
+      <c r="K111" s="5"/>
+      <c r="L111" s="5"/>
+      <c r="M111" s="5"/>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>46</v>
+      </c>
+      <c r="B112" t="s">
+        <v>10</v>
+      </c>
+      <c r="C112" t="s">
+        <v>7</v>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="H112" s="5"/>
+      <c r="I112" s="5"/>
+      <c r="J112" s="5"/>
+      <c r="K112" s="5"/>
+      <c r="L112" s="5"/>
+      <c r="M112" s="5"/>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>47</v>
+      </c>
+      <c r="B113" t="s">
+        <v>43</v>
+      </c>
+      <c r="C113" t="s">
+        <v>7</v>
+      </c>
+      <c r="D113">
+        <v>0</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="H113" s="5"/>
+      <c r="I113" s="5"/>
+      <c r="J113" s="5"/>
+      <c r="K113" s="5"/>
+      <c r="L113" s="5"/>
+      <c r="M113" s="5"/>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>47</v>
+      </c>
+      <c r="B114" t="s">
+        <v>44</v>
+      </c>
+      <c r="C114" t="s">
+        <v>7</v>
+      </c>
+      <c r="D114" t="s">
+        <v>29</v>
+      </c>
+      <c r="E114" t="s">
+        <v>33</v>
+      </c>
+      <c r="F114" t="s">
+        <v>33</v>
+      </c>
+      <c r="H114" s="5"/>
+      <c r="I114" s="5"/>
+      <c r="J114" s="5"/>
+      <c r="K114" s="5"/>
+      <c r="L114" s="5"/>
+      <c r="M114" s="5"/>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>47</v>
+      </c>
+      <c r="B115" t="s">
+        <v>9</v>
+      </c>
+      <c r="C115" t="s">
+        <v>7</v>
+      </c>
+      <c r="D115" t="s">
+        <v>32</v>
+      </c>
+      <c r="E115" t="s">
+        <v>29</v>
+      </c>
+      <c r="F115" t="s">
+        <v>29</v>
+      </c>
+      <c r="H115" s="5"/>
+      <c r="I115" s="5"/>
+      <c r="J115" s="5"/>
+      <c r="K115" s="5"/>
+      <c r="L115" s="5"/>
+      <c r="M115" s="5"/>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>47</v>
+      </c>
+      <c r="B116" t="s">
+        <v>10</v>
+      </c>
+      <c r="C116" t="s">
+        <v>7</v>
+      </c>
+      <c r="D116">
+        <v>0</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+      <c r="F116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>48</v>
+      </c>
+      <c r="B117" t="s">
+        <v>43</v>
+      </c>
+      <c r="C117" t="s">
+        <v>7</v>
+      </c>
+      <c r="D117">
+        <v>0</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>48</v>
+      </c>
+      <c r="B118" t="s">
+        <v>44</v>
+      </c>
+      <c r="C118" t="s">
+        <v>7</v>
+      </c>
+      <c r="D118" t="s">
+        <v>29</v>
+      </c>
+      <c r="E118" t="s">
+        <v>33</v>
+      </c>
+      <c r="F118" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>48</v>
+      </c>
+      <c r="B119" t="s">
+        <v>9</v>
+      </c>
+      <c r="C119" t="s">
+        <v>7</v>
+      </c>
+      <c r="D119" t="s">
+        <v>32</v>
+      </c>
+      <c r="E119" t="s">
+        <v>29</v>
+      </c>
+      <c r="F119" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>48</v>
+      </c>
+      <c r="B120" t="s">
+        <v>10</v>
+      </c>
+      <c r="C120" t="s">
+        <v>7</v>
+      </c>
+      <c r="D120">
+        <v>0</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+      <c r="F120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>49</v>
+      </c>
+      <c r="B121" t="s">
+        <v>43</v>
+      </c>
+      <c r="C121" t="s">
+        <v>7</v>
+      </c>
+      <c r="D121">
+        <v>0</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>49</v>
+      </c>
+      <c r="B122" t="s">
+        <v>44</v>
+      </c>
+      <c r="C122" t="s">
+        <v>7</v>
+      </c>
+      <c r="D122" t="s">
+        <v>29</v>
+      </c>
+      <c r="E122" t="s">
+        <v>33</v>
+      </c>
+      <c r="F122" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>49</v>
+      </c>
+      <c r="B123" t="s">
+        <v>9</v>
+      </c>
+      <c r="C123" t="s">
+        <v>7</v>
+      </c>
+      <c r="D123" t="s">
+        <v>32</v>
+      </c>
+      <c r="E123" t="s">
+        <v>29</v>
+      </c>
+      <c r="F123" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>49</v>
+      </c>
+      <c r="B124" t="s">
+        <v>10</v>
+      </c>
+      <c r="C124" t="s">
+        <v>7</v>
+      </c>
+      <c r="D124">
+        <v>0</v>
+      </c>
+      <c r="E124">
+        <v>0</v>
+      </c>
+      <c r="F124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>50</v>
+      </c>
+      <c r="B125" t="s">
+        <v>43</v>
+      </c>
+      <c r="C125" t="s">
+        <v>7</v>
+      </c>
+      <c r="D125">
+        <v>0</v>
+      </c>
+      <c r="E125">
+        <v>0</v>
+      </c>
+      <c r="F125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>50</v>
+      </c>
+      <c r="B126" t="s">
+        <v>44</v>
+      </c>
+      <c r="C126" t="s">
+        <v>7</v>
+      </c>
+      <c r="D126" t="s">
+        <v>29</v>
+      </c>
+      <c r="E126" t="s">
+        <v>33</v>
+      </c>
+      <c r="F126" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>50</v>
+      </c>
+      <c r="B127" t="s">
+        <v>9</v>
+      </c>
+      <c r="C127" t="s">
+        <v>7</v>
+      </c>
+      <c r="D127" t="s">
+        <v>32</v>
+      </c>
+      <c r="E127" t="s">
+        <v>29</v>
+      </c>
+      <c r="F127" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>50</v>
+      </c>
+      <c r="B128" t="s">
+        <v>10</v>
+      </c>
+      <c r="C128" t="s">
+        <v>7</v>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+      <c r="E128">
+        <v>0</v>
+      </c>
+      <c r="F128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>51</v>
+      </c>
+      <c r="B129" t="s">
+        <v>6</v>
+      </c>
+      <c r="C129" t="s">
+        <v>7</v>
+      </c>
+      <c r="D129" t="s">
+        <v>32</v>
+      </c>
+      <c r="E129" t="s">
+        <v>32</v>
+      </c>
+      <c r="F129" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>51</v>
+      </c>
+      <c r="B130" t="s">
+        <v>8</v>
+      </c>
+      <c r="C130" t="s">
+        <v>7</v>
+      </c>
+      <c r="D130" t="s">
+        <v>30</v>
+      </c>
+      <c r="E130" t="s">
+        <v>30</v>
+      </c>
+      <c r="F130" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>51</v>
+      </c>
+      <c r="B131" t="s">
+        <v>58</v>
+      </c>
+      <c r="C131" t="s">
+        <v>7</v>
+      </c>
+      <c r="D131" t="s">
+        <v>29</v>
+      </c>
+      <c r="E131" t="s">
+        <v>32</v>
+      </c>
+      <c r="F131" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>51</v>
+      </c>
+      <c r="B132" t="s">
+        <v>9</v>
+      </c>
+      <c r="C132" t="s">
+        <v>7</v>
+      </c>
+      <c r="D132" t="s">
+        <v>59</v>
+      </c>
+      <c r="E132" t="s">
+        <v>60</v>
+      </c>
+      <c r="F132" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>51</v>
+      </c>
+      <c r="B133" t="s">
+        <v>10</v>
+      </c>
+      <c r="C133" t="s">
+        <v>7</v>
+      </c>
+      <c r="D133">
+        <v>0</v>
+      </c>
+      <c r="E133">
+        <v>0</v>
+      </c>
+      <c r="F133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>52</v>
+      </c>
+      <c r="B134" t="s">
+        <v>6</v>
+      </c>
+      <c r="C134" t="s">
+        <v>7</v>
+      </c>
+      <c r="D134" t="s">
+        <v>32</v>
+      </c>
+      <c r="E134" t="s">
+        <v>32</v>
+      </c>
+      <c r="F134" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>52</v>
+      </c>
+      <c r="B135" t="s">
+        <v>8</v>
+      </c>
+      <c r="C135" t="s">
+        <v>7</v>
+      </c>
+      <c r="D135" t="s">
+        <v>30</v>
+      </c>
+      <c r="E135" t="s">
+        <v>30</v>
+      </c>
+      <c r="F135" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>52</v>
+      </c>
+      <c r="B136" t="s">
+        <v>58</v>
+      </c>
+      <c r="C136" t="s">
+        <v>7</v>
+      </c>
+      <c r="D136" t="s">
+        <v>29</v>
+      </c>
+      <c r="E136" t="s">
+        <v>32</v>
+      </c>
+      <c r="F136" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>52</v>
+      </c>
+      <c r="B137" t="s">
+        <v>9</v>
+      </c>
+      <c r="C137" t="s">
+        <v>7</v>
+      </c>
+      <c r="D137" t="s">
+        <v>59</v>
+      </c>
+      <c r="E137" t="s">
+        <v>60</v>
+      </c>
+      <c r="F137" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>52</v>
+      </c>
+      <c r="B138" t="s">
+        <v>10</v>
+      </c>
+      <c r="C138" t="s">
+        <v>7</v>
+      </c>
+      <c r="D138">
+        <v>0</v>
+      </c>
+      <c r="E138">
+        <v>0</v>
+      </c>
+      <c r="F138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>53</v>
+      </c>
+      <c r="B139" t="s">
+        <v>6</v>
+      </c>
+      <c r="C139" t="s">
+        <v>7</v>
+      </c>
+      <c r="D139" t="s">
+        <v>32</v>
+      </c>
+      <c r="E139" t="s">
+        <v>32</v>
+      </c>
+      <c r="F139" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>53</v>
+      </c>
+      <c r="B140" t="s">
+        <v>8</v>
+      </c>
+      <c r="C140" t="s">
+        <v>7</v>
+      </c>
+      <c r="D140" t="s">
+        <v>30</v>
+      </c>
+      <c r="E140" t="s">
+        <v>30</v>
+      </c>
+      <c r="F140" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>53</v>
+      </c>
+      <c r="B141" t="s">
+        <v>58</v>
+      </c>
+      <c r="C141" t="s">
+        <v>7</v>
+      </c>
+      <c r="D141" t="s">
+        <v>29</v>
+      </c>
+      <c r="E141" t="s">
+        <v>32</v>
+      </c>
+      <c r="F141" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>53</v>
+      </c>
+      <c r="B142" t="s">
+        <v>9</v>
+      </c>
+      <c r="C142" t="s">
+        <v>7</v>
+      </c>
+      <c r="D142" t="s">
+        <v>59</v>
+      </c>
+      <c r="E142" t="s">
+        <v>60</v>
+      </c>
+      <c r="F142" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>53</v>
+      </c>
+      <c r="B143" t="s">
+        <v>10</v>
+      </c>
+      <c r="C143" t="s">
+        <v>7</v>
+      </c>
+      <c r="D143">
+        <v>0</v>
+      </c>
+      <c r="E143">
+        <v>0</v>
+      </c>
+      <c r="F143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>54</v>
+      </c>
+      <c r="B144" t="s">
+        <v>6</v>
+      </c>
+      <c r="C144" t="s">
+        <v>7</v>
+      </c>
+      <c r="D144" t="s">
+        <v>32</v>
+      </c>
+      <c r="E144" t="s">
+        <v>32</v>
+      </c>
+      <c r="F144" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>54</v>
+      </c>
+      <c r="B145" t="s">
+        <v>8</v>
+      </c>
+      <c r="C145" t="s">
+        <v>7</v>
+      </c>
+      <c r="D145" t="s">
+        <v>30</v>
+      </c>
+      <c r="E145" t="s">
+        <v>30</v>
+      </c>
+      <c r="F145" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>54</v>
+      </c>
+      <c r="B146" t="s">
+        <v>58</v>
+      </c>
+      <c r="C146" t="s">
+        <v>7</v>
+      </c>
+      <c r="D146" t="s">
+        <v>29</v>
+      </c>
+      <c r="E146" t="s">
+        <v>32</v>
+      </c>
+      <c r="F146" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
+        <v>54</v>
+      </c>
+      <c r="B147" t="s">
+        <v>9</v>
+      </c>
+      <c r="C147" t="s">
+        <v>7</v>
+      </c>
+      <c r="D147" t="s">
+        <v>59</v>
+      </c>
+      <c r="E147" t="s">
+        <v>60</v>
+      </c>
+      <c r="F147" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
+        <v>54</v>
+      </c>
+      <c r="B148" t="s">
+        <v>10</v>
+      </c>
+      <c r="C148" t="s">
+        <v>7</v>
+      </c>
+      <c r="D148">
+        <v>0</v>
+      </c>
+      <c r="E148">
+        <v>0</v>
+      </c>
+      <c r="F148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
+        <v>55</v>
+      </c>
+      <c r="B149" t="s">
+        <v>6</v>
+      </c>
+      <c r="C149" t="s">
+        <v>7</v>
+      </c>
+      <c r="D149" t="s">
+        <v>32</v>
+      </c>
+      <c r="E149" t="s">
+        <v>32</v>
+      </c>
+      <c r="F149" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>55</v>
+      </c>
+      <c r="B150" t="s">
+        <v>8</v>
+      </c>
+      <c r="C150" t="s">
+        <v>7</v>
+      </c>
+      <c r="D150" t="s">
+        <v>30</v>
+      </c>
+      <c r="E150" t="s">
+        <v>30</v>
+      </c>
+      <c r="F150" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>55</v>
+      </c>
+      <c r="B151" t="s">
+        <v>58</v>
+      </c>
+      <c r="C151" t="s">
+        <v>7</v>
+      </c>
+      <c r="D151" t="s">
+        <v>29</v>
+      </c>
+      <c r="E151" t="s">
+        <v>32</v>
+      </c>
+      <c r="F151" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
+        <v>55</v>
+      </c>
+      <c r="B152" t="s">
+        <v>9</v>
+      </c>
+      <c r="C152" t="s">
+        <v>7</v>
+      </c>
+      <c r="D152" t="s">
+        <v>59</v>
+      </c>
+      <c r="E152" t="s">
+        <v>60</v>
+      </c>
+      <c r="F152" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
+        <v>55</v>
+      </c>
+      <c r="B153" t="s">
+        <v>10</v>
+      </c>
+      <c r="C153" t="s">
+        <v>7</v>
+      </c>
+      <c r="D153">
+        <v>0</v>
+      </c>
+      <c r="E153">
+        <v>0</v>
+      </c>
+      <c r="F153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>56</v>
+      </c>
+      <c r="B154" t="s">
+        <v>6</v>
+      </c>
+      <c r="C154" t="s">
+        <v>7</v>
+      </c>
+      <c r="D154" t="s">
+        <v>32</v>
+      </c>
+      <c r="E154" t="s">
+        <v>32</v>
+      </c>
+      <c r="F154" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>56</v>
+      </c>
+      <c r="B155" t="s">
+        <v>8</v>
+      </c>
+      <c r="C155" t="s">
+        <v>7</v>
+      </c>
+      <c r="D155" t="s">
+        <v>30</v>
+      </c>
+      <c r="E155" t="s">
+        <v>30</v>
+      </c>
+      <c r="F155" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>56</v>
+      </c>
+      <c r="B156" t="s">
+        <v>58</v>
+      </c>
+      <c r="C156" t="s">
+        <v>7</v>
+      </c>
+      <c r="D156" t="s">
+        <v>29</v>
+      </c>
+      <c r="E156" t="s">
+        <v>32</v>
+      </c>
+      <c r="F156" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
+        <v>56</v>
+      </c>
+      <c r="B157" t="s">
+        <v>9</v>
+      </c>
+      <c r="C157" t="s">
+        <v>7</v>
+      </c>
+      <c r="D157" t="s">
+        <v>59</v>
+      </c>
+      <c r="E157" t="s">
+        <v>60</v>
+      </c>
+      <c r="F157" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
+        <v>56</v>
+      </c>
+      <c r="B158" t="s">
+        <v>10</v>
+      </c>
+      <c r="C158" t="s">
+        <v>7</v>
+      </c>
+      <c r="D158">
+        <v>0</v>
+      </c>
+      <c r="E158">
+        <v>0</v>
+      </c>
+      <c r="F158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
+        <v>57</v>
+      </c>
+      <c r="B159" t="s">
+        <v>6</v>
+      </c>
+      <c r="C159" t="s">
+        <v>7</v>
+      </c>
+      <c r="D159" t="s">
+        <v>32</v>
+      </c>
+      <c r="E159" t="s">
+        <v>32</v>
+      </c>
+      <c r="F159" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
+        <v>57</v>
+      </c>
+      <c r="B160" t="s">
+        <v>8</v>
+      </c>
+      <c r="C160" t="s">
+        <v>7</v>
+      </c>
+      <c r="D160" t="s">
+        <v>30</v>
+      </c>
+      <c r="E160" t="s">
+        <v>30</v>
+      </c>
+      <c r="F160" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
+        <v>57</v>
+      </c>
+      <c r="B161" t="s">
+        <v>58</v>
+      </c>
+      <c r="C161" t="s">
+        <v>7</v>
+      </c>
+      <c r="D161" t="s">
+        <v>29</v>
+      </c>
+      <c r="E161" t="s">
+        <v>32</v>
+      </c>
+      <c r="F161" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
+        <v>57</v>
+      </c>
+      <c r="B162" t="s">
+        <v>9</v>
+      </c>
+      <c r="C162" t="s">
+        <v>7</v>
+      </c>
+      <c r="D162" t="s">
+        <v>59</v>
+      </c>
+      <c r="E162" t="s">
+        <v>60</v>
+      </c>
+      <c r="F162" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
+        <v>57</v>
+      </c>
+      <c r="B163" t="s">
+        <v>10</v>
+      </c>
+      <c r="C163" t="s">
+        <v>7</v>
+      </c>
+      <c r="D163">
+        <v>0</v>
+      </c>
+      <c r="E163">
+        <v>0</v>
+      </c>
+      <c r="F163">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/qtp_pyaez/data_input/crop_inputs/crop_specific_rule.xlsx
+++ b/qtp_pyaez/data_input/crop_inputs/crop_specific_rule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ming-mayhu/Desktop/毕业论文/qtp-pyaez/qtp_pyaez/data_input/crop_inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9323D3A7-2CDA-8D4A-9C29-6D1D3F02CAC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E41210-504F-B146-B3F5-EDC50CE27D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="680" windowWidth="25640" windowHeight="13980" xr2:uid="{FAED07CE-E758-F243-A6BC-F160777535F9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1125" uniqueCount="78">
   <si>
     <t>Crop</t>
   </si>
@@ -219,6 +219,57 @@
   </si>
   <si>
     <t>0.083*CY</t>
+  </si>
+  <si>
+    <t>spring_oat_128</t>
+  </si>
+  <si>
+    <t>spring_oat_129</t>
+  </si>
+  <si>
+    <t>spring_oat_130</t>
+  </si>
+  <si>
+    <t>L5a+L4a+L3a+L3b+L4b+L5b</t>
+  </si>
+  <si>
+    <t>dry_pea_189</t>
+  </si>
+  <si>
+    <t>dry_pea_190</t>
+  </si>
+  <si>
+    <t>dry_pea_191</t>
+  </si>
+  <si>
+    <t>L5b+L4b+L3b+L2b</t>
+  </si>
+  <si>
+    <t>winter_rape_216</t>
+  </si>
+  <si>
+    <t>winter_rape_217</t>
+  </si>
+  <si>
+    <t>winter_rape_218</t>
+  </si>
+  <si>
+    <t>winter_rape_219</t>
+  </si>
+  <si>
+    <t>spring_rape_220</t>
+  </si>
+  <si>
+    <t>spring_rape_221</t>
+  </si>
+  <si>
+    <t>spring_rape_222</t>
+  </si>
+  <si>
+    <t>spring_rape_223</t>
+  </si>
+  <si>
+    <t>0.500*CYb</t>
   </si>
 </sst>
 </file>
@@ -285,7 +336,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -295,11 +346,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -636,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0741791B-D8B1-7142-B84F-2E444F66886B}">
-  <dimension ref="A1:M163"/>
+  <dimension ref="A1:M226"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.33203125" customWidth="1"/>
@@ -2802,12 +2852,6 @@
       <c r="F106" t="s">
         <v>33</v>
       </c>
-      <c r="H106" s="5"/>
-      <c r="I106" s="5"/>
-      <c r="J106" s="5"/>
-      <c r="K106" s="5"/>
-      <c r="L106" s="5"/>
-      <c r="M106" s="5"/>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
@@ -2828,12 +2872,12 @@
       <c r="F107" t="s">
         <v>29</v>
       </c>
-      <c r="H107" s="7"/>
-      <c r="I107" s="6"/>
-      <c r="J107" s="6"/>
-      <c r="K107" s="6"/>
-      <c r="L107" s="6"/>
-      <c r="M107" s="6"/>
+      <c r="H107" s="6"/>
+      <c r="I107" s="5"/>
+      <c r="J107" s="5"/>
+      <c r="K107" s="5"/>
+      <c r="L107" s="5"/>
+      <c r="M107" s="5"/>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
@@ -2854,12 +2898,12 @@
       <c r="F108">
         <v>0</v>
       </c>
-      <c r="H108" s="7"/>
-      <c r="I108" s="6"/>
-      <c r="J108" s="6"/>
-      <c r="K108" s="6"/>
-      <c r="L108" s="6"/>
-      <c r="M108" s="6"/>
+      <c r="H108" s="6"/>
+      <c r="I108" s="5"/>
+      <c r="J108" s="5"/>
+      <c r="K108" s="5"/>
+      <c r="L108" s="5"/>
+      <c r="M108" s="5"/>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
@@ -2880,12 +2924,12 @@
       <c r="F109">
         <v>0</v>
       </c>
-      <c r="H109" s="7"/>
-      <c r="I109" s="6"/>
-      <c r="J109" s="6"/>
-      <c r="K109" s="6"/>
-      <c r="L109" s="6"/>
-      <c r="M109" s="6"/>
+      <c r="H109" s="6"/>
+      <c r="I109" s="5"/>
+      <c r="J109" s="5"/>
+      <c r="K109" s="5"/>
+      <c r="L109" s="5"/>
+      <c r="M109" s="5"/>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
@@ -2906,12 +2950,12 @@
       <c r="F110" t="s">
         <v>33</v>
       </c>
-      <c r="H110" s="7"/>
-      <c r="I110" s="6"/>
-      <c r="J110" s="6"/>
-      <c r="K110" s="6"/>
-      <c r="L110" s="6"/>
-      <c r="M110" s="6"/>
+      <c r="H110" s="6"/>
+      <c r="I110" s="5"/>
+      <c r="J110" s="5"/>
+      <c r="K110" s="5"/>
+      <c r="L110" s="5"/>
+      <c r="M110" s="5"/>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
@@ -2932,12 +2976,6 @@
       <c r="F111" t="s">
         <v>29</v>
       </c>
-      <c r="H111" s="5"/>
-      <c r="I111" s="5"/>
-      <c r="J111" s="5"/>
-      <c r="K111" s="5"/>
-      <c r="L111" s="5"/>
-      <c r="M111" s="5"/>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
@@ -2958,14 +2996,8 @@
       <c r="F112">
         <v>0</v>
       </c>
-      <c r="H112" s="5"/>
-      <c r="I112" s="5"/>
-      <c r="J112" s="5"/>
-      <c r="K112" s="5"/>
-      <c r="L112" s="5"/>
-      <c r="M112" s="5"/>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>47</v>
       </c>
@@ -2984,14 +3016,8 @@
       <c r="F113">
         <v>0</v>
       </c>
-      <c r="H113" s="5"/>
-      <c r="I113" s="5"/>
-      <c r="J113" s="5"/>
-      <c r="K113" s="5"/>
-      <c r="L113" s="5"/>
-      <c r="M113" s="5"/>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>47</v>
       </c>
@@ -3010,14 +3036,8 @@
       <c r="F114" t="s">
         <v>33</v>
       </c>
-      <c r="H114" s="5"/>
-      <c r="I114" s="5"/>
-      <c r="J114" s="5"/>
-      <c r="K114" s="5"/>
-      <c r="L114" s="5"/>
-      <c r="M114" s="5"/>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>47</v>
       </c>
@@ -3036,14 +3056,8 @@
       <c r="F115" t="s">
         <v>29</v>
       </c>
-      <c r="H115" s="5"/>
-      <c r="I115" s="5"/>
-      <c r="J115" s="5"/>
-      <c r="K115" s="5"/>
-      <c r="L115" s="5"/>
-      <c r="M115" s="5"/>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>47</v>
       </c>
@@ -3063,7 +3077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>48</v>
       </c>
@@ -3083,7 +3097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>48</v>
       </c>
@@ -3103,7 +3117,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>48</v>
       </c>
@@ -3123,7 +3137,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>48</v>
       </c>
@@ -3143,7 +3157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>49</v>
       </c>
@@ -3163,7 +3177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>49</v>
       </c>
@@ -3183,7 +3197,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>49</v>
       </c>
@@ -3203,7 +3217,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>49</v>
       </c>
@@ -3223,7 +3237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>50</v>
       </c>
@@ -3243,7 +3257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>50</v>
       </c>
@@ -3263,7 +3277,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>50</v>
       </c>
@@ -3283,7 +3297,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>50</v>
       </c>
@@ -4000,6 +4014,1266 @@
         <v>0</v>
       </c>
       <c r="F163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
+        <v>61</v>
+      </c>
+      <c r="B164" t="s">
+        <v>6</v>
+      </c>
+      <c r="C164" t="s">
+        <v>7</v>
+      </c>
+      <c r="D164" t="s">
+        <v>28</v>
+      </c>
+      <c r="E164" t="s">
+        <v>29</v>
+      </c>
+      <c r="F164" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>61</v>
+      </c>
+      <c r="B165" t="s">
+        <v>8</v>
+      </c>
+      <c r="C165" t="s">
+        <v>7</v>
+      </c>
+      <c r="D165">
+        <v>0</v>
+      </c>
+      <c r="E165">
+        <v>0</v>
+      </c>
+      <c r="F165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A166" t="s">
+        <v>61</v>
+      </c>
+      <c r="B166" t="s">
+        <v>21</v>
+      </c>
+      <c r="C166" t="s">
+        <v>12</v>
+      </c>
+      <c r="D166" t="s">
+        <v>30</v>
+      </c>
+      <c r="E166" t="s">
+        <v>30</v>
+      </c>
+      <c r="F166" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A167" t="s">
+        <v>61</v>
+      </c>
+      <c r="B167" t="s">
+        <v>9</v>
+      </c>
+      <c r="C167" t="s">
+        <v>7</v>
+      </c>
+      <c r="D167" t="s">
+        <v>32</v>
+      </c>
+      <c r="E167" t="s">
+        <v>32</v>
+      </c>
+      <c r="F167" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A168" t="s">
+        <v>61</v>
+      </c>
+      <c r="B168" t="s">
+        <v>10</v>
+      </c>
+      <c r="C168" t="s">
+        <v>7</v>
+      </c>
+      <c r="D168">
+        <v>0</v>
+      </c>
+      <c r="E168">
+        <v>0</v>
+      </c>
+      <c r="F168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A169" t="s">
+        <v>62</v>
+      </c>
+      <c r="B169" t="s">
+        <v>6</v>
+      </c>
+      <c r="C169" t="s">
+        <v>7</v>
+      </c>
+      <c r="D169" t="s">
+        <v>28</v>
+      </c>
+      <c r="E169" t="s">
+        <v>29</v>
+      </c>
+      <c r="F169" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A170" t="s">
+        <v>62</v>
+      </c>
+      <c r="B170" t="s">
+        <v>8</v>
+      </c>
+      <c r="C170" t="s">
+        <v>7</v>
+      </c>
+      <c r="D170">
+        <v>0</v>
+      </c>
+      <c r="E170">
+        <v>0</v>
+      </c>
+      <c r="F170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A171" t="s">
+        <v>62</v>
+      </c>
+      <c r="B171" t="s">
+        <v>21</v>
+      </c>
+      <c r="C171" t="s">
+        <v>12</v>
+      </c>
+      <c r="D171" t="s">
+        <v>30</v>
+      </c>
+      <c r="E171" t="s">
+        <v>30</v>
+      </c>
+      <c r="F171" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A172" t="s">
+        <v>62</v>
+      </c>
+      <c r="B172" t="s">
+        <v>9</v>
+      </c>
+      <c r="C172" t="s">
+        <v>7</v>
+      </c>
+      <c r="D172" t="s">
+        <v>32</v>
+      </c>
+      <c r="E172" t="s">
+        <v>32</v>
+      </c>
+      <c r="F172" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A173" t="s">
+        <v>62</v>
+      </c>
+      <c r="B173" t="s">
+        <v>10</v>
+      </c>
+      <c r="C173" t="s">
+        <v>7</v>
+      </c>
+      <c r="D173">
+        <v>0</v>
+      </c>
+      <c r="E173">
+        <v>0</v>
+      </c>
+      <c r="F173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A174" t="s">
+        <v>63</v>
+      </c>
+      <c r="B174" t="s">
+        <v>6</v>
+      </c>
+      <c r="C174" t="s">
+        <v>7</v>
+      </c>
+      <c r="D174" t="s">
+        <v>28</v>
+      </c>
+      <c r="E174" t="s">
+        <v>29</v>
+      </c>
+      <c r="F174" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A175" t="s">
+        <v>63</v>
+      </c>
+      <c r="B175" t="s">
+        <v>8</v>
+      </c>
+      <c r="C175" t="s">
+        <v>7</v>
+      </c>
+      <c r="D175">
+        <v>0</v>
+      </c>
+      <c r="E175">
+        <v>0</v>
+      </c>
+      <c r="F175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A176" t="s">
+        <v>63</v>
+      </c>
+      <c r="B176" t="s">
+        <v>21</v>
+      </c>
+      <c r="C176" t="s">
+        <v>12</v>
+      </c>
+      <c r="D176" t="s">
+        <v>30</v>
+      </c>
+      <c r="E176" t="s">
+        <v>30</v>
+      </c>
+      <c r="F176" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A177" t="s">
+        <v>63</v>
+      </c>
+      <c r="B177" t="s">
+        <v>9</v>
+      </c>
+      <c r="C177" t="s">
+        <v>7</v>
+      </c>
+      <c r="D177" t="s">
+        <v>32</v>
+      </c>
+      <c r="E177" t="s">
+        <v>32</v>
+      </c>
+      <c r="F177" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A178" t="s">
+        <v>63</v>
+      </c>
+      <c r="B178" t="s">
+        <v>10</v>
+      </c>
+      <c r="C178" t="s">
+        <v>7</v>
+      </c>
+      <c r="D178">
+        <v>0</v>
+      </c>
+      <c r="E178">
+        <v>0</v>
+      </c>
+      <c r="F178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A179" t="s">
+        <v>65</v>
+      </c>
+      <c r="B179" t="s">
+        <v>43</v>
+      </c>
+      <c r="C179" t="s">
+        <v>7</v>
+      </c>
+      <c r="D179">
+        <v>0</v>
+      </c>
+      <c r="E179">
+        <v>0</v>
+      </c>
+      <c r="F179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A180" t="s">
+        <v>65</v>
+      </c>
+      <c r="B180" t="s">
+        <v>44</v>
+      </c>
+      <c r="C180" t="s">
+        <v>7</v>
+      </c>
+      <c r="D180" t="s">
+        <v>33</v>
+      </c>
+      <c r="E180" t="s">
+        <v>33</v>
+      </c>
+      <c r="F180" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A181" t="s">
+        <v>65</v>
+      </c>
+      <c r="B181" t="s">
+        <v>64</v>
+      </c>
+      <c r="C181" t="s">
+        <v>12</v>
+      </c>
+      <c r="D181" t="s">
+        <v>33</v>
+      </c>
+      <c r="E181" t="s">
+        <v>29</v>
+      </c>
+      <c r="F181" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A182" t="s">
+        <v>65</v>
+      </c>
+      <c r="B182" t="s">
+        <v>10</v>
+      </c>
+      <c r="C182" t="s">
+        <v>7</v>
+      </c>
+      <c r="D182">
+        <v>0</v>
+      </c>
+      <c r="E182">
+        <v>0</v>
+      </c>
+      <c r="F182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A183" t="s">
+        <v>66</v>
+      </c>
+      <c r="B183" t="s">
+        <v>43</v>
+      </c>
+      <c r="C183" t="s">
+        <v>7</v>
+      </c>
+      <c r="D183">
+        <v>0</v>
+      </c>
+      <c r="E183">
+        <v>0</v>
+      </c>
+      <c r="F183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A184" t="s">
+        <v>66</v>
+      </c>
+      <c r="B184" t="s">
+        <v>44</v>
+      </c>
+      <c r="C184" t="s">
+        <v>7</v>
+      </c>
+      <c r="D184" t="s">
+        <v>33</v>
+      </c>
+      <c r="E184" t="s">
+        <v>33</v>
+      </c>
+      <c r="F184" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A185" t="s">
+        <v>66</v>
+      </c>
+      <c r="B185" t="s">
+        <v>64</v>
+      </c>
+      <c r="C185" t="s">
+        <v>12</v>
+      </c>
+      <c r="D185" t="s">
+        <v>33</v>
+      </c>
+      <c r="E185" t="s">
+        <v>29</v>
+      </c>
+      <c r="F185" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A186" t="s">
+        <v>66</v>
+      </c>
+      <c r="B186" t="s">
+        <v>10</v>
+      </c>
+      <c r="C186" t="s">
+        <v>7</v>
+      </c>
+      <c r="D186">
+        <v>0</v>
+      </c>
+      <c r="E186">
+        <v>0</v>
+      </c>
+      <c r="F186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A187" t="s">
+        <v>67</v>
+      </c>
+      <c r="B187" t="s">
+        <v>43</v>
+      </c>
+      <c r="C187" t="s">
+        <v>7</v>
+      </c>
+      <c r="D187">
+        <v>0</v>
+      </c>
+      <c r="E187">
+        <v>0</v>
+      </c>
+      <c r="F187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A188" t="s">
+        <v>67</v>
+      </c>
+      <c r="B188" t="s">
+        <v>44</v>
+      </c>
+      <c r="C188" t="s">
+        <v>7</v>
+      </c>
+      <c r="D188" t="s">
+        <v>33</v>
+      </c>
+      <c r="E188" t="s">
+        <v>33</v>
+      </c>
+      <c r="F188" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A189" t="s">
+        <v>67</v>
+      </c>
+      <c r="B189" t="s">
+        <v>64</v>
+      </c>
+      <c r="C189" t="s">
+        <v>12</v>
+      </c>
+      <c r="D189" t="s">
+        <v>33</v>
+      </c>
+      <c r="E189" t="s">
+        <v>29</v>
+      </c>
+      <c r="F189" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A190" t="s">
+        <v>67</v>
+      </c>
+      <c r="B190" t="s">
+        <v>10</v>
+      </c>
+      <c r="C190" t="s">
+        <v>7</v>
+      </c>
+      <c r="D190">
+        <v>0</v>
+      </c>
+      <c r="E190">
+        <v>0</v>
+      </c>
+      <c r="F190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A191" t="s">
+        <v>69</v>
+      </c>
+      <c r="B191" t="s">
+        <v>6</v>
+      </c>
+      <c r="C191" t="s">
+        <v>7</v>
+      </c>
+      <c r="D191" t="s">
+        <v>77</v>
+      </c>
+      <c r="E191" t="s">
+        <v>18</v>
+      </c>
+      <c r="F191" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A192" t="s">
+        <v>69</v>
+      </c>
+      <c r="B192" t="s">
+        <v>8</v>
+      </c>
+      <c r="C192" t="s">
+        <v>7</v>
+      </c>
+      <c r="D192">
+        <v>0</v>
+      </c>
+      <c r="E192">
+        <v>0</v>
+      </c>
+      <c r="F192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A193" t="s">
+        <v>69</v>
+      </c>
+      <c r="B193" t="s">
+        <v>68</v>
+      </c>
+      <c r="C193" t="s">
+        <v>7</v>
+      </c>
+      <c r="D193" t="s">
+        <v>77</v>
+      </c>
+      <c r="E193" t="s">
+        <v>77</v>
+      </c>
+      <c r="F193" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A194" t="s">
+        <v>69</v>
+      </c>
+      <c r="B194" t="s">
+        <v>9</v>
+      </c>
+      <c r="C194" t="s">
+        <v>7</v>
+      </c>
+      <c r="D194" t="s">
+        <v>19</v>
+      </c>
+      <c r="E194" t="s">
+        <v>19</v>
+      </c>
+      <c r="F194" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A195" t="s">
+        <v>69</v>
+      </c>
+      <c r="B195" t="s">
+        <v>10</v>
+      </c>
+      <c r="C195" t="s">
+        <v>7</v>
+      </c>
+      <c r="D195">
+        <v>0</v>
+      </c>
+      <c r="E195">
+        <v>0</v>
+      </c>
+      <c r="F195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A196" t="s">
+        <v>70</v>
+      </c>
+      <c r="B196" t="s">
+        <v>6</v>
+      </c>
+      <c r="C196" t="s">
+        <v>7</v>
+      </c>
+      <c r="D196" t="s">
+        <v>77</v>
+      </c>
+      <c r="E196" t="s">
+        <v>18</v>
+      </c>
+      <c r="F196" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A197" t="s">
+        <v>70</v>
+      </c>
+      <c r="B197" t="s">
+        <v>8</v>
+      </c>
+      <c r="C197" t="s">
+        <v>7</v>
+      </c>
+      <c r="D197">
+        <v>0</v>
+      </c>
+      <c r="E197">
+        <v>0</v>
+      </c>
+      <c r="F197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A198" t="s">
+        <v>70</v>
+      </c>
+      <c r="B198" t="s">
+        <v>68</v>
+      </c>
+      <c r="C198" t="s">
+        <v>7</v>
+      </c>
+      <c r="D198" t="s">
+        <v>77</v>
+      </c>
+      <c r="E198" t="s">
+        <v>77</v>
+      </c>
+      <c r="F198" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
+        <v>70</v>
+      </c>
+      <c r="B199" t="s">
+        <v>9</v>
+      </c>
+      <c r="C199" t="s">
+        <v>7</v>
+      </c>
+      <c r="D199" t="s">
+        <v>19</v>
+      </c>
+      <c r="E199" t="s">
+        <v>19</v>
+      </c>
+      <c r="F199" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A200" t="s">
+        <v>70</v>
+      </c>
+      <c r="B200" t="s">
+        <v>10</v>
+      </c>
+      <c r="C200" t="s">
+        <v>7</v>
+      </c>
+      <c r="D200">
+        <v>0</v>
+      </c>
+      <c r="E200">
+        <v>0</v>
+      </c>
+      <c r="F200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A201" t="s">
+        <v>71</v>
+      </c>
+      <c r="B201" t="s">
+        <v>6</v>
+      </c>
+      <c r="C201" t="s">
+        <v>7</v>
+      </c>
+      <c r="D201" t="s">
+        <v>77</v>
+      </c>
+      <c r="E201" t="s">
+        <v>18</v>
+      </c>
+      <c r="F201" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A202" t="s">
+        <v>71</v>
+      </c>
+      <c r="B202" t="s">
+        <v>8</v>
+      </c>
+      <c r="C202" t="s">
+        <v>7</v>
+      </c>
+      <c r="D202">
+        <v>0</v>
+      </c>
+      <c r="E202">
+        <v>0</v>
+      </c>
+      <c r="F202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A203" t="s">
+        <v>71</v>
+      </c>
+      <c r="B203" t="s">
+        <v>68</v>
+      </c>
+      <c r="C203" t="s">
+        <v>7</v>
+      </c>
+      <c r="D203" t="s">
+        <v>77</v>
+      </c>
+      <c r="E203" t="s">
+        <v>77</v>
+      </c>
+      <c r="F203" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A204" t="s">
+        <v>71</v>
+      </c>
+      <c r="B204" t="s">
+        <v>9</v>
+      </c>
+      <c r="C204" t="s">
+        <v>7</v>
+      </c>
+      <c r="D204" t="s">
+        <v>19</v>
+      </c>
+      <c r="E204" t="s">
+        <v>19</v>
+      </c>
+      <c r="F204" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A205" t="s">
+        <v>71</v>
+      </c>
+      <c r="B205" t="s">
+        <v>10</v>
+      </c>
+      <c r="C205" t="s">
+        <v>7</v>
+      </c>
+      <c r="D205">
+        <v>0</v>
+      </c>
+      <c r="E205">
+        <v>0</v>
+      </c>
+      <c r="F205">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A206" t="s">
+        <v>72</v>
+      </c>
+      <c r="B206" t="s">
+        <v>6</v>
+      </c>
+      <c r="C206" t="s">
+        <v>7</v>
+      </c>
+      <c r="D206" t="s">
+        <v>77</v>
+      </c>
+      <c r="E206" t="s">
+        <v>18</v>
+      </c>
+      <c r="F206" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A207" t="s">
+        <v>72</v>
+      </c>
+      <c r="B207" t="s">
+        <v>8</v>
+      </c>
+      <c r="C207" t="s">
+        <v>7</v>
+      </c>
+      <c r="D207">
+        <v>0</v>
+      </c>
+      <c r="E207">
+        <v>0</v>
+      </c>
+      <c r="F207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A208" t="s">
+        <v>72</v>
+      </c>
+      <c r="B208" t="s">
+        <v>68</v>
+      </c>
+      <c r="C208" t="s">
+        <v>7</v>
+      </c>
+      <c r="D208" t="s">
+        <v>77</v>
+      </c>
+      <c r="E208" t="s">
+        <v>77</v>
+      </c>
+      <c r="F208" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A209" t="s">
+        <v>72</v>
+      </c>
+      <c r="B209" t="s">
+        <v>9</v>
+      </c>
+      <c r="C209" t="s">
+        <v>7</v>
+      </c>
+      <c r="D209" t="s">
+        <v>19</v>
+      </c>
+      <c r="E209" t="s">
+        <v>19</v>
+      </c>
+      <c r="F209" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A210" t="s">
+        <v>72</v>
+      </c>
+      <c r="B210" t="s">
+        <v>10</v>
+      </c>
+      <c r="C210" t="s">
+        <v>7</v>
+      </c>
+      <c r="D210">
+        <v>0</v>
+      </c>
+      <c r="E210">
+        <v>0</v>
+      </c>
+      <c r="F210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A211" t="s">
+        <v>73</v>
+      </c>
+      <c r="B211" t="s">
+        <v>6</v>
+      </c>
+      <c r="C211" t="s">
+        <v>7</v>
+      </c>
+      <c r="D211" t="s">
+        <v>32</v>
+      </c>
+      <c r="E211" t="s">
+        <v>29</v>
+      </c>
+      <c r="F211" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A212" t="s">
+        <v>73</v>
+      </c>
+      <c r="B212" t="s">
+        <v>9</v>
+      </c>
+      <c r="C212" t="s">
+        <v>7</v>
+      </c>
+      <c r="D212" t="s">
+        <v>32</v>
+      </c>
+      <c r="E212" t="s">
+        <v>32</v>
+      </c>
+      <c r="F212" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A213" t="s">
+        <v>73</v>
+      </c>
+      <c r="B213" t="s">
+        <v>11</v>
+      </c>
+      <c r="C213" t="s">
+        <v>7</v>
+      </c>
+      <c r="D213" t="s">
+        <v>29</v>
+      </c>
+      <c r="E213" t="s">
+        <v>29</v>
+      </c>
+      <c r="F213" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A214" t="s">
+        <v>73</v>
+      </c>
+      <c r="B214" t="s">
+        <v>10</v>
+      </c>
+      <c r="C214" t="s">
+        <v>7</v>
+      </c>
+      <c r="D214">
+        <v>0</v>
+      </c>
+      <c r="E214">
+        <v>0</v>
+      </c>
+      <c r="F214">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A215" t="s">
+        <v>74</v>
+      </c>
+      <c r="B215" t="s">
+        <v>6</v>
+      </c>
+      <c r="C215" t="s">
+        <v>7</v>
+      </c>
+      <c r="D215" t="s">
+        <v>32</v>
+      </c>
+      <c r="E215" t="s">
+        <v>29</v>
+      </c>
+      <c r="F215" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A216" t="s">
+        <v>74</v>
+      </c>
+      <c r="B216" t="s">
+        <v>9</v>
+      </c>
+      <c r="C216" t="s">
+        <v>7</v>
+      </c>
+      <c r="D216" t="s">
+        <v>32</v>
+      </c>
+      <c r="E216" t="s">
+        <v>32</v>
+      </c>
+      <c r="F216" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A217" t="s">
+        <v>74</v>
+      </c>
+      <c r="B217" t="s">
+        <v>11</v>
+      </c>
+      <c r="C217" t="s">
+        <v>7</v>
+      </c>
+      <c r="D217" t="s">
+        <v>29</v>
+      </c>
+      <c r="E217" t="s">
+        <v>29</v>
+      </c>
+      <c r="F217" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A218" t="s">
+        <v>74</v>
+      </c>
+      <c r="B218" t="s">
+        <v>10</v>
+      </c>
+      <c r="C218" t="s">
+        <v>7</v>
+      </c>
+      <c r="D218">
+        <v>0</v>
+      </c>
+      <c r="E218">
+        <v>0</v>
+      </c>
+      <c r="F218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A219" t="s">
+        <v>75</v>
+      </c>
+      <c r="B219" t="s">
+        <v>6</v>
+      </c>
+      <c r="C219" t="s">
+        <v>7</v>
+      </c>
+      <c r="D219" t="s">
+        <v>32</v>
+      </c>
+      <c r="E219" t="s">
+        <v>29</v>
+      </c>
+      <c r="F219" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A220" t="s">
+        <v>75</v>
+      </c>
+      <c r="B220" t="s">
+        <v>9</v>
+      </c>
+      <c r="C220" t="s">
+        <v>7</v>
+      </c>
+      <c r="D220" t="s">
+        <v>32</v>
+      </c>
+      <c r="E220" t="s">
+        <v>32</v>
+      </c>
+      <c r="F220" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A221" t="s">
+        <v>75</v>
+      </c>
+      <c r="B221" t="s">
+        <v>11</v>
+      </c>
+      <c r="C221" t="s">
+        <v>7</v>
+      </c>
+      <c r="D221" t="s">
+        <v>29</v>
+      </c>
+      <c r="E221" t="s">
+        <v>29</v>
+      </c>
+      <c r="F221" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A222" t="s">
+        <v>75</v>
+      </c>
+      <c r="B222" t="s">
+        <v>10</v>
+      </c>
+      <c r="C222" t="s">
+        <v>7</v>
+      </c>
+      <c r="D222">
+        <v>0</v>
+      </c>
+      <c r="E222">
+        <v>0</v>
+      </c>
+      <c r="F222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A223" t="s">
+        <v>76</v>
+      </c>
+      <c r="B223" t="s">
+        <v>6</v>
+      </c>
+      <c r="C223" t="s">
+        <v>7</v>
+      </c>
+      <c r="D223" t="s">
+        <v>32</v>
+      </c>
+      <c r="E223" t="s">
+        <v>29</v>
+      </c>
+      <c r="F223" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A224" t="s">
+        <v>76</v>
+      </c>
+      <c r="B224" t="s">
+        <v>9</v>
+      </c>
+      <c r="C224" t="s">
+        <v>7</v>
+      </c>
+      <c r="D224" t="s">
+        <v>32</v>
+      </c>
+      <c r="E224" t="s">
+        <v>32</v>
+      </c>
+      <c r="F224" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A225" t="s">
+        <v>76</v>
+      </c>
+      <c r="B225" t="s">
+        <v>11</v>
+      </c>
+      <c r="C225" t="s">
+        <v>7</v>
+      </c>
+      <c r="D225" t="s">
+        <v>29</v>
+      </c>
+      <c r="E225" t="s">
+        <v>29</v>
+      </c>
+      <c r="F225" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A226" t="s">
+        <v>76</v>
+      </c>
+      <c r="B226" t="s">
+        <v>10</v>
+      </c>
+      <c r="C226" t="s">
+        <v>7</v>
+      </c>
+      <c r="D226">
+        <v>0</v>
+      </c>
+      <c r="E226">
+        <v>0</v>
+      </c>
+      <c r="F226">
         <v>0</v>
       </c>
     </row>
